--- a/Template/BusinessAutomationTools_Template.xlsx
+++ b/Template/BusinessAutomationTools_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floriansetojosesatoshi/Documents/20仕事/70独立/40 システム開発/02 開発関連/00テンプレート/01要件定義/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floriansetojosesatoshi/Development/BusinessAutomationTools/Template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710B04D8-98C5-B74F-95C6-CA1F05752728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A44B7A-38FC-E444-81EC-87E367DC82D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19560" xr2:uid="{FE744E13-58AD-3746-BA7C-E3290E428FD0}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19480" firstSheet="1" activeTab="16" xr2:uid="{FE744E13-58AD-3746-BA7C-E3290E428FD0}"/>
   </bookViews>
   <sheets>
     <sheet name="プロパティ" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="103">
   <si>
     <t>作成日</t>
     <rPh sb="0" eb="3">
@@ -205,10 +205,6 @@
     <rPh sb="0" eb="2">
       <t>タイショウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>No</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -581,6 +577,152 @@
     <t>改善点</t>
     <rPh sb="0" eb="3">
       <t>カイゼn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題No</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K002</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K003</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K004</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K005</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要求一覧</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要求No</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R002</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R003</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R004</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R005</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R006</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R007</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>R008</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能No</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F001</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F002</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F003</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F004</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F005</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F006</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F007</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作方法</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面構成</t>
+    <rPh sb="0" eb="4">
+      <t>ガメn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>桁数</t>
+    <rPh sb="0" eb="2">
+      <t>ケタスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性能</t>
+    <rPh sb="0" eb="2">
+      <t>セイノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要求定義</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テイギ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -672,7 +814,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -890,13 +1032,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1011,9 +1233,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1076,6 +1295,72 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1491,20 +1776,20 @@
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="48"/>
+      <c r="E2" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="47"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
@@ -1513,20 +1798,20 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="48"/>
+      <c r="E3" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="46"/>
+      <c r="P3" s="47"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
@@ -1535,20 +1820,20 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="48"/>
+      <c r="E4" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="47"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
@@ -1557,20 +1842,20 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="49" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="51"/>
+      <c r="E5" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="50"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
@@ -1579,142 +1864,142 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="48"/>
+      <c r="E6" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
+      <c r="P6" s="47"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="48"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="47"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="48"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="47"/>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="48"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="47"/>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="3"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="48"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="46"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="46"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="46"/>
+      <c r="P10" s="47"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="48"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="47"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="3"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="48"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="E2:P2"/>
+    <mergeCell ref="E5:P5"/>
+    <mergeCell ref="E6:P6"/>
+    <mergeCell ref="E7:P7"/>
+    <mergeCell ref="E8:P8"/>
     <mergeCell ref="E10:P10"/>
     <mergeCell ref="E11:P11"/>
     <mergeCell ref="E12:P12"/>
     <mergeCell ref="E3:P3"/>
     <mergeCell ref="E4:P4"/>
     <mergeCell ref="E9:P9"/>
-    <mergeCell ref="E2:P2"/>
-    <mergeCell ref="E5:P5"/>
-    <mergeCell ref="E6:P6"/>
-    <mergeCell ref="E7:P7"/>
-    <mergeCell ref="E8:P8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1723,15 +2008,15 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D903599-12DF-AA4A-86F9-B79546AC8BF5}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -1763,14 +2048,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -1802,51 +2089,78 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="B5" s="41"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="B6" s="41"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="B7" s="41"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="B8" s="41"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="B9" s="41"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="B10" s="41"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="B11" s="41"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="B12" s="41"/>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="B13" s="41"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="B14" s="41"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="B15" s="41"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="B16" s="41"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="40"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="40"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="B6" s="40"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="B7" s="40"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="B8" s="40"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="B9" s="40"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="40"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="40"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="B12" s="40"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="B13" s="40"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="B14" s="40"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="40"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="40"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="B17" s="39"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1860,15 +2174,15 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AB2126E-D2AD-4745-93A7-8F2D0E71A22E}">
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -1900,14 +2214,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -1939,34 +2255,36 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
       <c r="A4" s="8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="21" thickBot="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="21" thickBot="1">
       <c r="A5" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="D5" s="15"/>
       <c r="E5" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
-      <c r="K5" s="39" t="s">
-        <v>48</v>
+      <c r="K5" s="38" t="s">
+        <v>47</v>
       </c>
       <c r="L5" s="15"/>
       <c r="M5" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
@@ -1981,10 +2299,12 @@
       <c r="X5" s="14"/>
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="15"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="38"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="15"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="61"/>
       <c r="B6" s="32"/>
       <c r="C6" s="32"/>
       <c r="D6" s="33"/>
@@ -1997,7 +2317,7 @@
       <c r="K6" s="31"/>
       <c r="L6" s="33"/>
       <c r="M6" s="32"/>
-      <c r="N6" s="43"/>
+      <c r="N6" s="42"/>
       <c r="O6" s="32"/>
       <c r="P6" s="32"/>
       <c r="Q6" s="32"/>
@@ -2010,10 +2330,12 @@
       <c r="X6" s="32"/>
       <c r="Y6" s="32"/>
       <c r="Z6" s="32"/>
-      <c r="AA6" s="33"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="36"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="62"/>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
       <c r="D7" s="21"/>
@@ -2026,7 +2348,7 @@
       <c r="K7" s="19"/>
       <c r="L7" s="21"/>
       <c r="M7" s="20"/>
-      <c r="N7" s="42"/>
+      <c r="N7" s="41"/>
       <c r="O7" s="20"/>
       <c r="P7" s="20"/>
       <c r="Q7" s="20"/>
@@ -2039,10 +2361,12 @@
       <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="36"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="62"/>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
       <c r="D8" s="21"/>
@@ -2055,7 +2379,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="21"/>
       <c r="M8" s="20"/>
-      <c r="N8" s="42"/>
+      <c r="N8" s="41"/>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
       <c r="Q8" s="20"/>
@@ -2068,10 +2392,12 @@
       <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="36"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="62"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
       <c r="D9" s="21"/>
@@ -2084,7 +2410,7 @@
       <c r="K9" s="19"/>
       <c r="L9" s="21"/>
       <c r="M9" s="20"/>
-      <c r="N9" s="42"/>
+      <c r="N9" s="41"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
@@ -2097,10 +2423,12 @@
       <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="36"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="62"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="21"/>
@@ -2113,7 +2441,7 @@
       <c r="K10" s="19"/>
       <c r="L10" s="21"/>
       <c r="M10" s="20"/>
-      <c r="N10" s="42"/>
+      <c r="N10" s="41"/>
       <c r="O10" s="20"/>
       <c r="P10" s="20"/>
       <c r="Q10" s="20"/>
@@ -2126,9 +2454,400 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="62"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="62"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29" ht="21" thickBot="1">
+      <c r="A13" s="63"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="23"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0021B3-9A52-744A-B795-C09790A6FF2C}">
+  <dimension ref="A1:AC13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="9" t="str">
+        <f>ProjectName</f>
+        <v>【〇〇システム構築プロジェクト】</v>
+      </c>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="V1" s="14"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="9" t="str" cm="1">
+        <f t="array" aca="1" ref="X1" ca="1">INDIRECT("02_改版履歴!F"&amp;CELL("row", _xlfn.XLOOKUP(MAX(ModNoRange), ModNoRange, ModNoRange)))</f>
+        <v>【日付】</v>
+      </c>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="5" t="str">
+        <f>SystemName</f>
+        <v>【システム】</v>
+      </c>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="17"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="5" t="str" cm="1">
+        <f t="array" aca="1" ref="X2" ca="1">INDIRECT("02_改版履歴!I"&amp;CELL("row", _xlfn.XLOOKUP(MAX(ModNoRange), ModNoRange, ModNoRange)))</f>
+        <v>【名前】</v>
+      </c>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
+      <c r="A4" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="21" thickBot="1">
+      <c r="A5" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="15"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="61"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="62"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="62"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="62"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="62"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="36"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -2142,7 +2861,7 @@
       <c r="K11" s="19"/>
       <c r="L11" s="21"/>
       <c r="M11" s="20"/>
-      <c r="N11" s="42"/>
+      <c r="N11" s="41"/>
       <c r="O11" s="20"/>
       <c r="P11" s="20"/>
       <c r="Q11" s="20"/>
@@ -2155,9 +2874,11 @@
       <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="36"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -2171,7 +2892,7 @@
       <c r="K12" s="19"/>
       <c r="L12" s="21"/>
       <c r="M12" s="20"/>
-      <c r="N12" s="42"/>
+      <c r="N12" s="41"/>
       <c r="O12" s="20"/>
       <c r="P12" s="20"/>
       <c r="Q12" s="20"/>
@@ -2184,9 +2905,11 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27" ht="21" thickBot="1">
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29" ht="21" thickBot="1">
       <c r="A13" s="37"/>
       <c r="B13" s="23"/>
       <c r="C13" s="23"/>
@@ -2213,7 +2936,9 @@
       <c r="X13" s="23"/>
       <c r="Y13" s="23"/>
       <c r="Z13" s="23"/>
-      <c r="AA13" s="24"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2225,17 +2950,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0021B3-9A52-744A-B795-C09790A6FF2C}">
-  <dimension ref="A1:AA13"/>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE9743F-1511-8545-B242-F71766D91493}">
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -2267,14 +2992,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -2306,37 +3033,41 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
       <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="21" thickBot="1">
-      <c r="A5" s="12" t="s">
-        <v>45</v>
+    <row r="5" spans="1:29" ht="21" thickBot="1">
+      <c r="A5" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="14" t="s">
-        <v>47</v>
+      <c r="D5" s="14"/>
+      <c r="E5" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="39" t="s">
-        <v>48</v>
+      <c r="J5" s="15"/>
+      <c r="K5" s="38" t="s">
+        <v>47</v>
       </c>
       <c r="L5" s="15"/>
-      <c r="M5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
+      <c r="M5" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="N5" s="15"/>
+      <c r="O5" s="14" t="s">
+        <v>21</v>
+      </c>
       <c r="P5" s="14"/>
       <c r="Q5" s="14"/>
       <c r="R5" s="14"/>
@@ -2348,23 +3079,25 @@
       <c r="X5" s="14"/>
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="15"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="38"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="15"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="31"/>
       <c r="B6" s="32"/>
       <c r="C6" s="32"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="32"/>
       <c r="G6" s="32"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
+      <c r="J6" s="33"/>
       <c r="K6" s="31"/>
       <c r="L6" s="33"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="43"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="33"/>
       <c r="O6" s="32"/>
       <c r="P6" s="32"/>
       <c r="Q6" s="32"/>
@@ -2377,23 +3110,25 @@
       <c r="X6" s="32"/>
       <c r="Y6" s="32"/>
       <c r="Z6" s="32"/>
-      <c r="AA6" s="33"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="36"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="J7" s="21"/>
       <c r="K7" s="19"/>
       <c r="L7" s="21"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="42"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="21"/>
       <c r="O7" s="20"/>
       <c r="P7" s="20"/>
       <c r="Q7" s="20"/>
@@ -2406,23 +3141,25 @@
       <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="36"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
+      <c r="J8" s="21"/>
       <c r="K8" s="19"/>
       <c r="L8" s="21"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="42"/>
+      <c r="M8" s="80"/>
+      <c r="N8" s="21"/>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
       <c r="Q8" s="20"/>
@@ -2435,23 +3172,25 @@
       <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="36"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="19"/>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
+      <c r="J9" s="21"/>
       <c r="K9" s="19"/>
       <c r="L9" s="21"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="42"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="21"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
@@ -2464,23 +3203,25 @@
       <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="36"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="19"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="19"/>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
+      <c r="J10" s="21"/>
       <c r="K10" s="19"/>
       <c r="L10" s="21"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="42"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="21"/>
       <c r="O10" s="20"/>
       <c r="P10" s="20"/>
       <c r="Q10" s="20"/>
@@ -2493,23 +3234,25 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="36"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="19"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="19"/>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
+      <c r="J11" s="21"/>
       <c r="K11" s="19"/>
       <c r="L11" s="21"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="42"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="21"/>
       <c r="O11" s="20"/>
       <c r="P11" s="20"/>
       <c r="Q11" s="20"/>
@@ -2522,23 +3265,25 @@
       <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="36"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="19"/>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
+      <c r="J12" s="21"/>
       <c r="K12" s="19"/>
       <c r="L12" s="21"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="42"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="21"/>
       <c r="O12" s="20"/>
       <c r="P12" s="20"/>
       <c r="Q12" s="20"/>
@@ -2551,36 +3296,288 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27" ht="21" thickBot="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="24"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="21"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="21"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="21"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="21"/>
+    </row>
+    <row r="17" spans="1:29">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="21"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="21"/>
+    </row>
+    <row r="18" spans="1:29">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="21"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="21"/>
+    </row>
+    <row r="19" spans="1:29">
+      <c r="A19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="21"/>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="21"/>
+    </row>
+    <row r="21" spans="1:29" ht="21" thickBot="1">
+      <c r="A21" s="22"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="23"/>
+      <c r="W21" s="23"/>
+      <c r="X21" s="23"/>
+      <c r="Y21" s="23"/>
+      <c r="Z21" s="23"/>
+      <c r="AA21" s="23"/>
+      <c r="AB21" s="23"/>
+      <c r="AC21" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2592,17 +3589,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE9743F-1511-8545-B242-F71766D91493}">
-  <dimension ref="A1:AA21"/>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5128DCFC-3540-C441-BD79-62285C7BA9B4}">
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -2634,14 +3631,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -2673,513 +3672,111 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="21" thickBot="1">
-      <c r="A5" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="8"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="15"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="31"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="33"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="19"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="20"/>
-      <c r="X11" s="20"/>
-      <c r="Y11" s="20"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="20"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="20"/>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="20"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="20"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="20"/>
-      <c r="Z13" s="20"/>
-      <c r="AA13" s="21"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20"/>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="20"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="21"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="20"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="21"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="X16" s="20"/>
-      <c r="Y16" s="20"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="21"/>
-    </row>
-    <row r="17" spans="1:27">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20"/>
-      <c r="X17" s="20"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="21"/>
-    </row>
-    <row r="18" spans="1:27">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20"/>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="21"/>
-    </row>
-    <row r="19" spans="1:27">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="20"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20"/>
-      <c r="X19" s="20"/>
-      <c r="Y19" s="20"/>
-      <c r="Z19" s="20"/>
-      <c r="AA19" s="21"/>
-    </row>
-    <row r="20" spans="1:27">
-      <c r="A20" s="19"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="21"/>
-    </row>
-    <row r="21" spans="1:27" ht="21" thickBot="1">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="23"/>
-      <c r="P21" s="23"/>
-      <c r="Q21" s="23"/>
-      <c r="R21" s="23"/>
-      <c r="S21" s="23"/>
-      <c r="T21" s="23"/>
-      <c r="U21" s="23"/>
-      <c r="V21" s="23"/>
-      <c r="W21" s="23"/>
-      <c r="X21" s="23"/>
-      <c r="Y21" s="23"/>
-      <c r="Z21" s="23"/>
-      <c r="AA21" s="24"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="8"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="8"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="8"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3191,17 +3788,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5128DCFC-3540-C441-BD79-62285C7BA9B4}">
-  <dimension ref="A1:AA18"/>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261A3D33-3407-A342-B73F-B4A30E3EEEC9}">
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -3233,14 +3830,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -3272,46 +3871,84 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="39"/>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="8" t="s">
-        <v>71</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="39" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="8" t="s">
-        <v>54</v>
+      <c r="A18" s="39"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="39" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3324,17 +3961,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261A3D33-3407-A342-B73F-B4A30E3EEEC9}">
-  <dimension ref="A1:AA23"/>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B13C21-6044-E54B-8B6F-406C63639072}">
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -3366,14 +4003,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -3405,83 +4044,81 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="A5" s="40" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:29">
       <c r="A7" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="40"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="40" t="s">
+    <row r="10" spans="1:29">
+      <c r="A10" s="43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:29">
       <c r="A13" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:29">
       <c r="A16" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="40" t="s">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="40"/>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="40" t="s">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
     </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="39"/>
+    </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="40" t="s">
-        <v>17</v>
-      </c>
+      <c r="A22" s="8"/>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="8"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3493,17 +4130,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B13C21-6044-E54B-8B6F-406C63639072}">
-  <dimension ref="A1:AA34"/>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{223653DE-793D-AF46-B501-44461604D87A}">
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -3535,14 +4172,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -3574,154 +4213,18 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
       <c r="A4" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="A5" s="40"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="40"/>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="8"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="40"/>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="40"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{223653DE-793D-AF46-B501-44461604D87A}">
-  <dimension ref="A1:AA30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
-  <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="9" t="str">
-        <f>ProjectName</f>
-        <v>【〇〇システム構築プロジェクト】</v>
-      </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="V1" s="14"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="9" t="str" cm="1">
-        <f t="array" aca="1" ref="X1" ca="1">INDIRECT("02_改版履歴!F"&amp;CELL("row", _xlfn.XLOOKUP(MAX(ModNoRange), ModNoRange, ModNoRange)))</f>
-        <v>【日付】</v>
-      </c>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="5" t="str">
-        <f>SystemName</f>
-        <v>【システム】</v>
-      </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" s="17"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="5" t="str" cm="1">
-        <f t="array" aca="1" ref="X2" ca="1">INDIRECT("02_改版履歴!I"&amp;CELL("row", _xlfn.XLOOKUP(MAX(ModNoRange), ModNoRange, ModNoRange)))</f>
-        <v>【名前】</v>
-      </c>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
-      <c r="A4" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="21" thickBot="1">
+      <c r="A5" s="13" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="21" thickBot="1">
-      <c r="A5" s="13" t="s">
-        <v>74</v>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
@@ -3734,7 +4237,7 @@
       <c r="J5" s="35"/>
       <c r="K5" s="35"/>
       <c r="L5" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M5" s="35"/>
       <c r="N5" s="35"/>
@@ -3746,15 +4249,17 @@
       <c r="T5" s="35"/>
       <c r="U5" s="35"/>
       <c r="V5" s="35"/>
-      <c r="W5" s="34"/>
-      <c r="X5" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="34"/>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="W5" s="60"/>
+      <c r="X5" s="60"/>
+      <c r="Y5" s="34"/>
+      <c r="Z5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="35"/>
+      <c r="AC5" s="34"/>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="31"/>
       <c r="B6" s="32"/>
       <c r="C6" s="32"/>
@@ -3777,13 +4282,15 @@
       <c r="T6" s="32"/>
       <c r="U6" s="32"/>
       <c r="V6" s="32"/>
-      <c r="W6" s="33"/>
+      <c r="W6" s="32"/>
       <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="33"/>
-    </row>
-    <row r="7" spans="1:27">
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="42"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="19"/>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -3806,13 +4313,15 @@
       <c r="T7" s="20"/>
       <c r="U7" s="20"/>
       <c r="V7" s="20"/>
-      <c r="W7" s="21"/>
+      <c r="W7" s="20"/>
       <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="41"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="19"/>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -3835,13 +4344,15 @@
       <c r="T8" s="20"/>
       <c r="U8" s="20"/>
       <c r="V8" s="20"/>
-      <c r="W8" s="21"/>
+      <c r="W8" s="20"/>
       <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="41"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="19"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -3864,14 +4375,16 @@
       <c r="T9" s="20"/>
       <c r="U9" s="20"/>
       <c r="V9" s="20"/>
-      <c r="W9" s="21"/>
+      <c r="W9" s="20"/>
       <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="45"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="41"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="44"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
@@ -3893,13 +4406,15 @@
       <c r="T10" s="20"/>
       <c r="U10" s="20"/>
       <c r="V10" s="20"/>
-      <c r="W10" s="21"/>
+      <c r="W10" s="20"/>
       <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
+      <c r="Y10" s="21"/>
       <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="36"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -3922,13 +4437,15 @@
       <c r="T11" s="20"/>
       <c r="U11" s="20"/>
       <c r="V11" s="20"/>
-      <c r="W11" s="21"/>
+      <c r="W11" s="20"/>
       <c r="X11" s="20"/>
-      <c r="Y11" s="20"/>
+      <c r="Y11" s="21"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="19"/>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -3951,14 +4468,16 @@
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
       <c r="V12" s="20"/>
-      <c r="W12" s="21"/>
+      <c r="W12" s="20"/>
       <c r="X12" s="20"/>
-      <c r="Y12" s="20"/>
+      <c r="Y12" s="21"/>
       <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="45"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="44"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
       <c r="D13" s="20"/>
@@ -3980,13 +4499,15 @@
       <c r="T13" s="20"/>
       <c r="U13" s="20"/>
       <c r="V13" s="20"/>
-      <c r="W13" s="21"/>
+      <c r="W13" s="20"/>
       <c r="X13" s="20"/>
-      <c r="Y13" s="20"/>
+      <c r="Y13" s="21"/>
       <c r="Z13" s="20"/>
-      <c r="AA13" s="21"/>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="21"/>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -4009,13 +4530,15 @@
       <c r="T14" s="20"/>
       <c r="U14" s="20"/>
       <c r="V14" s="20"/>
-      <c r="W14" s="21"/>
+      <c r="W14" s="20"/>
       <c r="X14" s="20"/>
-      <c r="Y14" s="20"/>
+      <c r="Y14" s="21"/>
       <c r="Z14" s="20"/>
-      <c r="AA14" s="21"/>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="21"/>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -4038,14 +4561,16 @@
       <c r="T15" s="20"/>
       <c r="U15" s="20"/>
       <c r="V15" s="20"/>
-      <c r="W15" s="21"/>
+      <c r="W15" s="20"/>
       <c r="X15" s="20"/>
-      <c r="Y15" s="20"/>
+      <c r="Y15" s="21"/>
       <c r="Z15" s="20"/>
-      <c r="AA15" s="21"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="45"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="21"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="44"/>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
@@ -4067,13 +4592,15 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
       <c r="V16" s="20"/>
-      <c r="W16" s="21"/>
+      <c r="W16" s="20"/>
       <c r="X16" s="20"/>
-      <c r="Y16" s="20"/>
+      <c r="Y16" s="21"/>
       <c r="Z16" s="20"/>
-      <c r="AA16" s="21"/>
-    </row>
-    <row r="17" spans="1:27">
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="21"/>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="19"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -4096,14 +4623,16 @@
       <c r="T17" s="20"/>
       <c r="U17" s="20"/>
       <c r="V17" s="20"/>
-      <c r="W17" s="21"/>
+      <c r="W17" s="20"/>
       <c r="X17" s="20"/>
-      <c r="Y17" s="20"/>
+      <c r="Y17" s="21"/>
       <c r="Z17" s="20"/>
-      <c r="AA17" s="21"/>
-    </row>
-    <row r="18" spans="1:27">
-      <c r="A18" s="45"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="21"/>
+    </row>
+    <row r="18" spans="1:29">
+      <c r="A18" s="44"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
       <c r="D18" s="20"/>
@@ -4125,13 +4654,15 @@
       <c r="T18" s="20"/>
       <c r="U18" s="20"/>
       <c r="V18" s="20"/>
-      <c r="W18" s="21"/>
+      <c r="W18" s="20"/>
       <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
+      <c r="Y18" s="21"/>
       <c r="Z18" s="20"/>
-      <c r="AA18" s="21"/>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="21"/>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="36"/>
       <c r="B19" s="20"/>
       <c r="C19" s="20"/>
@@ -4154,13 +4685,15 @@
       <c r="T19" s="20"/>
       <c r="U19" s="20"/>
       <c r="V19" s="20"/>
-      <c r="W19" s="21"/>
+      <c r="W19" s="20"/>
       <c r="X19" s="20"/>
-      <c r="Y19" s="20"/>
+      <c r="Y19" s="21"/>
       <c r="Z19" s="20"/>
-      <c r="AA19" s="21"/>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="21"/>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -4183,13 +4716,15 @@
       <c r="T20" s="20"/>
       <c r="U20" s="20"/>
       <c r="V20" s="20"/>
-      <c r="W20" s="21"/>
+      <c r="W20" s="20"/>
       <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
+      <c r="Y20" s="21"/>
       <c r="Z20" s="20"/>
-      <c r="AA20" s="21"/>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="21"/>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -4212,13 +4747,15 @@
       <c r="T21" s="20"/>
       <c r="U21" s="20"/>
       <c r="V21" s="20"/>
-      <c r="W21" s="21"/>
+      <c r="W21" s="20"/>
       <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
+      <c r="Y21" s="21"/>
       <c r="Z21" s="20"/>
-      <c r="AA21" s="21"/>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="21"/>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -4241,13 +4778,15 @@
       <c r="T22" s="20"/>
       <c r="U22" s="20"/>
       <c r="V22" s="20"/>
-      <c r="W22" s="21"/>
+      <c r="W22" s="20"/>
       <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
+      <c r="Y22" s="21"/>
       <c r="Z22" s="20"/>
-      <c r="AA22" s="21"/>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="21"/>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="19"/>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -4270,13 +4809,15 @@
       <c r="T23" s="20"/>
       <c r="U23" s="20"/>
       <c r="V23" s="20"/>
-      <c r="W23" s="21"/>
+      <c r="W23" s="20"/>
       <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
+      <c r="Y23" s="21"/>
       <c r="Z23" s="20"/>
-      <c r="AA23" s="21"/>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="21"/>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="19"/>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -4299,13 +4840,15 @@
       <c r="T24" s="20"/>
       <c r="U24" s="20"/>
       <c r="V24" s="20"/>
-      <c r="W24" s="21"/>
+      <c r="W24" s="20"/>
       <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
+      <c r="Y24" s="21"/>
       <c r="Z24" s="20"/>
-      <c r="AA24" s="21"/>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="21"/>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="19"/>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -4328,13 +4871,15 @@
       <c r="T25" s="20"/>
       <c r="U25" s="20"/>
       <c r="V25" s="20"/>
-      <c r="W25" s="21"/>
+      <c r="W25" s="20"/>
       <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
+      <c r="Y25" s="21"/>
       <c r="Z25" s="20"/>
-      <c r="AA25" s="21"/>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="21"/>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="19"/>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -4357,13 +4902,15 @@
       <c r="T26" s="20"/>
       <c r="U26" s="20"/>
       <c r="V26" s="20"/>
-      <c r="W26" s="21"/>
+      <c r="W26" s="20"/>
       <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
+      <c r="Y26" s="21"/>
       <c r="Z26" s="20"/>
-      <c r="AA26" s="21"/>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="21"/>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -4386,13 +4933,15 @@
       <c r="T27" s="20"/>
       <c r="U27" s="20"/>
       <c r="V27" s="20"/>
-      <c r="W27" s="21"/>
+      <c r="W27" s="20"/>
       <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
+      <c r="Y27" s="21"/>
       <c r="Z27" s="20"/>
-      <c r="AA27" s="21"/>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="21"/>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="19"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -4415,13 +4964,15 @@
       <c r="T28" s="20"/>
       <c r="U28" s="20"/>
       <c r="V28" s="20"/>
-      <c r="W28" s="21"/>
+      <c r="W28" s="20"/>
       <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
+      <c r="Y28" s="21"/>
       <c r="Z28" s="20"/>
-      <c r="AA28" s="21"/>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="21"/>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -4444,13 +4995,15 @@
       <c r="T29" s="20"/>
       <c r="U29" s="20"/>
       <c r="V29" s="20"/>
-      <c r="W29" s="21"/>
+      <c r="W29" s="20"/>
       <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
+      <c r="Y29" s="21"/>
       <c r="Z29" s="20"/>
-      <c r="AA29" s="21"/>
-    </row>
-    <row r="30" spans="1:27" ht="21" thickBot="1">
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="21"/>
+    </row>
+    <row r="30" spans="1:29" ht="21" thickBot="1">
       <c r="A30" s="22"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23"/>
@@ -4473,11 +5026,13 @@
       <c r="T30" s="23"/>
       <c r="U30" s="23"/>
       <c r="V30" s="23"/>
-      <c r="W30" s="24"/>
+      <c r="W30" s="23"/>
       <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
+      <c r="Y30" s="24"/>
       <c r="Z30" s="23"/>
-      <c r="AA30" s="24"/>
+      <c r="AA30" s="23"/>
+      <c r="AB30" s="23"/>
+      <c r="AC30" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4495,101 +5050,101 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
     <row r="7" spans="3:23" ht="54">
-      <c r="E7" s="53" t="str">
+      <c r="E7" s="52" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
       </c>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="53"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="53"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="53"/>
-      <c r="U7" s="53"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="52"/>
     </row>
     <row r="12" spans="3:23">
       <c r="C12" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="52" t="str">
+      <c r="G12" s="51" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
       </c>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="52"/>
-      <c r="W12" s="52"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
     </row>
     <row r="14" spans="3:23">
       <c r="C14" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="52" t="str">
+      <c r="G14" s="51" t="str">
         <f>ProgramName</f>
         <v>【プログラム】</v>
       </c>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="52"/>
-      <c r="W14" s="52"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="51"/>
+      <c r="S14" s="51"/>
+      <c r="T14" s="51"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="51"/>
     </row>
     <row r="16" spans="3:23">
       <c r="C16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="52" t="str" cm="1">
+        <v>22</v>
+      </c>
+      <c r="G16" s="51" t="str" cm="1">
         <f t="array" aca="1" ref="G16" ca="1">TEXT(INDIRECT("02_改版履歴!C"&amp;CELL("row", _xlfn.XLOOKUP(MAX(ModNoRange), ModNoRange, ModNoRange))),"0.0.0")</f>
         <v>0.1.0</v>
       </c>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="52"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="52"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="52"/>
-      <c r="R16" s="52"/>
-      <c r="S16" s="52"/>
-      <c r="T16" s="52"/>
-      <c r="U16" s="52"/>
-      <c r="V16" s="52"/>
-      <c r="W16" s="52"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="51"/>
+      <c r="S16" s="51"/>
+      <c r="T16" s="51"/>
+      <c r="U16" s="51"/>
+      <c r="V16" s="51"/>
+      <c r="W16" s="51"/>
     </row>
     <row r="18" spans="7:19">
       <c r="G18" s="4" t="s">
@@ -4633,7 +5188,7 @@
     </row>
     <row r="20" spans="7:19">
       <c r="G20" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="3"/>
@@ -4658,7 +5213,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="3"/>
       <c r="J21" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -4686,15 +5241,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D384FF48-6ADC-7546-B13A-DA9331911FFF}">
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -4726,14 +5281,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -4765,16 +5322,18 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="3" spans="1:27" ht="21" thickBot="1"/>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="3" spans="1:29" ht="21" thickBot="1"/>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
       <c r="A4" s="13" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="34"/>
       <c r="C4" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" s="35"/>
       <c r="E4" s="35"/>
@@ -4809,9 +5368,11 @@
       <c r="X4" s="35"/>
       <c r="Y4" s="35"/>
       <c r="Z4" s="35"/>
-      <c r="AA4" s="34"/>
-    </row>
-    <row r="5" spans="1:27">
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="34"/>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="29">
         <v>1</v>
       </c>
@@ -4854,9 +5415,11 @@
       <c r="X5" s="32"/>
       <c r="Y5" s="32"/>
       <c r="Z5" s="32"/>
-      <c r="AA5" s="33"/>
-    </row>
-    <row r="6" spans="1:27">
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="33"/>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="25"/>
       <c r="B6" s="26"/>
       <c r="C6" s="19"/>
@@ -4883,9 +5446,11 @@
       <c r="X6" s="20"/>
       <c r="Y6" s="20"/>
       <c r="Z6" s="20"/>
-      <c r="AA6" s="21"/>
-    </row>
-    <row r="7" spans="1:27">
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="21"/>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="25"/>
       <c r="B7" s="26"/>
       <c r="C7" s="19"/>
@@ -4912,9 +5477,11 @@
       <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="25"/>
       <c r="B8" s="26"/>
       <c r="C8" s="19"/>
@@ -4941,9 +5508,11 @@
       <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="25"/>
       <c r="B9" s="26"/>
       <c r="C9" s="19"/>
@@ -4970,9 +5539,11 @@
       <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="25"/>
       <c r="B10" s="26"/>
       <c r="C10" s="19"/>
@@ -4999,9 +5570,11 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="25"/>
       <c r="B11" s="26"/>
       <c r="C11" s="19"/>
@@ -5028,9 +5601,11 @@
       <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="25"/>
       <c r="B12" s="26"/>
       <c r="C12" s="19"/>
@@ -5057,9 +5632,11 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27">
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="25"/>
       <c r="B13" s="26"/>
       <c r="C13" s="19"/>
@@ -5086,9 +5663,11 @@
       <c r="X13" s="20"/>
       <c r="Y13" s="20"/>
       <c r="Z13" s="20"/>
-      <c r="AA13" s="21"/>
-    </row>
-    <row r="14" spans="1:27">
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="21"/>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="25"/>
       <c r="B14" s="26"/>
       <c r="C14" s="19"/>
@@ -5115,9 +5694,11 @@
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
       <c r="Z14" s="20"/>
-      <c r="AA14" s="21"/>
-    </row>
-    <row r="15" spans="1:27">
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="21"/>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="25"/>
       <c r="B15" s="26"/>
       <c r="C15" s="19"/>
@@ -5144,9 +5725,11 @@
       <c r="X15" s="20"/>
       <c r="Y15" s="20"/>
       <c r="Z15" s="20"/>
-      <c r="AA15" s="21"/>
-    </row>
-    <row r="16" spans="1:27">
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="21"/>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="25"/>
       <c r="B16" s="26"/>
       <c r="C16" s="19"/>
@@ -5173,9 +5756,11 @@
       <c r="X16" s="20"/>
       <c r="Y16" s="20"/>
       <c r="Z16" s="20"/>
-      <c r="AA16" s="21"/>
-    </row>
-    <row r="17" spans="1:27">
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="21"/>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="25"/>
       <c r="B17" s="26"/>
       <c r="C17" s="19"/>
@@ -5202,9 +5787,11 @@
       <c r="X17" s="20"/>
       <c r="Y17" s="20"/>
       <c r="Z17" s="20"/>
-      <c r="AA17" s="21"/>
-    </row>
-    <row r="18" spans="1:27">
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="21"/>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="25"/>
       <c r="B18" s="26"/>
       <c r="C18" s="19"/>
@@ -5231,9 +5818,11 @@
       <c r="X18" s="20"/>
       <c r="Y18" s="20"/>
       <c r="Z18" s="20"/>
-      <c r="AA18" s="21"/>
-    </row>
-    <row r="19" spans="1:27">
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="21"/>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="25"/>
       <c r="B19" s="26"/>
       <c r="C19" s="19"/>
@@ -5260,9 +5849,11 @@
       <c r="X19" s="20"/>
       <c r="Y19" s="20"/>
       <c r="Z19" s="20"/>
-      <c r="AA19" s="21"/>
-    </row>
-    <row r="20" spans="1:27">
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="21"/>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="25"/>
       <c r="B20" s="26"/>
       <c r="C20" s="19"/>
@@ -5289,9 +5880,11 @@
       <c r="X20" s="20"/>
       <c r="Y20" s="20"/>
       <c r="Z20" s="20"/>
-      <c r="AA20" s="21"/>
-    </row>
-    <row r="21" spans="1:27">
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="21"/>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="25"/>
       <c r="B21" s="26"/>
       <c r="C21" s="19"/>
@@ -5318,9 +5911,11 @@
       <c r="X21" s="20"/>
       <c r="Y21" s="20"/>
       <c r="Z21" s="20"/>
-      <c r="AA21" s="21"/>
-    </row>
-    <row r="22" spans="1:27">
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="21"/>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="25"/>
       <c r="B22" s="26"/>
       <c r="C22" s="19"/>
@@ -5347,9 +5942,11 @@
       <c r="X22" s="20"/>
       <c r="Y22" s="20"/>
       <c r="Z22" s="20"/>
-      <c r="AA22" s="21"/>
-    </row>
-    <row r="23" spans="1:27">
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="21"/>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="25"/>
       <c r="B23" s="26"/>
       <c r="C23" s="19"/>
@@ -5376,9 +5973,11 @@
       <c r="X23" s="20"/>
       <c r="Y23" s="20"/>
       <c r="Z23" s="20"/>
-      <c r="AA23" s="21"/>
-    </row>
-    <row r="24" spans="1:27">
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="21"/>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="25"/>
       <c r="B24" s="26"/>
       <c r="C24" s="19"/>
@@ -5405,9 +6004,11 @@
       <c r="X24" s="20"/>
       <c r="Y24" s="20"/>
       <c r="Z24" s="20"/>
-      <c r="AA24" s="21"/>
-    </row>
-    <row r="25" spans="1:27">
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="21"/>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="25"/>
       <c r="B25" s="26"/>
       <c r="C25" s="19"/>
@@ -5434,9 +6035,11 @@
       <c r="X25" s="20"/>
       <c r="Y25" s="20"/>
       <c r="Z25" s="20"/>
-      <c r="AA25" s="21"/>
-    </row>
-    <row r="26" spans="1:27">
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="21"/>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="25"/>
       <c r="B26" s="26"/>
       <c r="C26" s="19"/>
@@ -5463,9 +6066,11 @@
       <c r="X26" s="20"/>
       <c r="Y26" s="20"/>
       <c r="Z26" s="20"/>
-      <c r="AA26" s="21"/>
-    </row>
-    <row r="27" spans="1:27">
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="21"/>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="25"/>
       <c r="B27" s="26"/>
       <c r="C27" s="19"/>
@@ -5492,9 +6097,11 @@
       <c r="X27" s="20"/>
       <c r="Y27" s="20"/>
       <c r="Z27" s="20"/>
-      <c r="AA27" s="21"/>
-    </row>
-    <row r="28" spans="1:27">
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="21"/>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="25"/>
       <c r="B28" s="26"/>
       <c r="C28" s="19"/>
@@ -5521,9 +6128,11 @@
       <c r="X28" s="20"/>
       <c r="Y28" s="20"/>
       <c r="Z28" s="20"/>
-      <c r="AA28" s="21"/>
-    </row>
-    <row r="29" spans="1:27">
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="21"/>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="25"/>
       <c r="B29" s="26"/>
       <c r="C29" s="19"/>
@@ -5550,9 +6159,11 @@
       <c r="X29" s="20"/>
       <c r="Y29" s="20"/>
       <c r="Z29" s="20"/>
-      <c r="AA29" s="21"/>
-    </row>
-    <row r="30" spans="1:27" ht="21" thickBot="1">
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="21"/>
+    </row>
+    <row r="30" spans="1:29" ht="21" thickBot="1">
       <c r="A30" s="27"/>
       <c r="B30" s="28"/>
       <c r="C30" s="22"/>
@@ -5579,7 +6190,9 @@
       <c r="X30" s="23"/>
       <c r="Y30" s="23"/>
       <c r="Z30" s="23"/>
-      <c r="AA30" s="24"/>
+      <c r="AA30" s="23"/>
+      <c r="AB30" s="23"/>
+      <c r="AC30" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5593,15 +6206,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3F9E76-DB0E-DA45-B74F-11D5C5B49F0A}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -5633,14 +6246,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -5672,55 +6287,57 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="A5" s="40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:29">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:29">
+      <c r="A8" s="39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:29">
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="40" t="s">
+    <row r="11" spans="1:29">
+      <c r="A11" s="39" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:29">
       <c r="A13" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="A16" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="39" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5736,15 +6353,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49956457-1539-C64C-B35C-81993878239B}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -5776,14 +6393,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -5815,51 +6434,53 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="B5" s="41"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="B6" s="41"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="B7" s="41"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="B8" s="41"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="B9" s="41"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="B10" s="41"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="B11" s="41"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="B12" s="41"/>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="B13" s="41"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="B14" s="41"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="B15" s="41"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="B16" s="41"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="B5" s="40"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="B6" s="40"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="B7" s="40"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="B8" s="40"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="B9" s="40"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="B10" s="40"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="B11" s="40"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="B12" s="40"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="B13" s="40"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="B14" s="40"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="B15" s="40"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="B16" s="40"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="40"/>
+      <c r="B17" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5873,15 +6494,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D76D768-0064-3B4E-8246-20FA62D3418F}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -5913,14 +6534,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -5952,34 +6575,36 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
       <c r="A4" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="8"/>
     </row>
-    <row r="5" spans="1:27" ht="21" thickBot="1">
-      <c r="A5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="14"/>
+    <row r="5" spans="1:29" ht="21" thickBot="1">
+      <c r="A5" s="59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="38" t="s">
+        <v>37</v>
+      </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+      <c r="H5" s="60"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
-      <c r="K5" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="38" t="s">
+        <v>36</v>
+      </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
@@ -5990,17 +6615,21 @@
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
       <c r="W5" s="14"/>
-      <c r="X5" s="15"/>
-      <c r="Y5" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="15"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="38"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32"/>
+      <c r="X5" s="14"/>
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="15"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="32"/>
@@ -6008,12 +6637,12 @@
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="J6" s="32"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="43"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="32"/>
       <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
+      <c r="P6" s="42"/>
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32"/>
@@ -6021,15 +6650,19 @@
       <c r="U6" s="32"/>
       <c r="V6" s="32"/>
       <c r="W6" s="32"/>
-      <c r="X6" s="33"/>
+      <c r="X6" s="32"/>
       <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="33"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="36"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
@@ -6037,12 +6670,12 @@
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="42"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
       <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
+      <c r="P7" s="41"/>
       <c r="Q7" s="20"/>
       <c r="R7" s="20"/>
       <c r="S7" s="20"/>
@@ -6050,15 +6683,19 @@
       <c r="U7" s="20"/>
       <c r="V7" s="20"/>
       <c r="W7" s="20"/>
-      <c r="X7" s="21"/>
+      <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="36"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -6066,12 +6703,12 @@
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
       <c r="J8" s="20"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="42"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="20"/>
       <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
+      <c r="P8" s="41"/>
       <c r="Q8" s="20"/>
       <c r="R8" s="20"/>
       <c r="S8" s="20"/>
@@ -6079,15 +6716,19 @@
       <c r="U8" s="20"/>
       <c r="V8" s="20"/>
       <c r="W8" s="20"/>
-      <c r="X8" s="21"/>
+      <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="36"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
@@ -6095,12 +6736,12 @@
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="42"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="20"/>
       <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
+      <c r="P9" s="41"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
@@ -6108,15 +6749,19 @@
       <c r="U9" s="20"/>
       <c r="V9" s="20"/>
       <c r="W9" s="20"/>
-      <c r="X9" s="21"/>
+      <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="36"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
@@ -6124,12 +6769,12 @@
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="42"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="20"/>
       <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
+      <c r="P10" s="41"/>
       <c r="Q10" s="20"/>
       <c r="R10" s="20"/>
       <c r="S10" s="20"/>
@@ -6137,15 +6782,17 @@
       <c r="U10" s="20"/>
       <c r="V10" s="20"/>
       <c r="W10" s="20"/>
-      <c r="X10" s="21"/>
+      <c r="X10" s="20"/>
       <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="36"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="62"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
@@ -6153,12 +6800,12 @@
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="42"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="20"/>
       <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
+      <c r="P11" s="41"/>
       <c r="Q11" s="20"/>
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
@@ -6166,15 +6813,17 @@
       <c r="U11" s="20"/>
       <c r="V11" s="20"/>
       <c r="W11" s="20"/>
-      <c r="X11" s="21"/>
+      <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
-      <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="36"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="62"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
@@ -6182,12 +6831,12 @@
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="42"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
+      <c r="P12" s="41"/>
       <c r="Q12" s="20"/>
       <c r="R12" s="20"/>
       <c r="S12" s="20"/>
@@ -6195,15 +6844,17 @@
       <c r="U12" s="20"/>
       <c r="V12" s="20"/>
       <c r="W12" s="20"/>
-      <c r="X12" s="21"/>
+      <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
-      <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27" ht="21" thickBot="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29" ht="21" thickBot="1">
+      <c r="A13" s="63"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
@@ -6211,9 +6862,9 @@
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="22"/>
       <c r="N13" s="23"/>
       <c r="O13" s="23"/>
       <c r="P13" s="23"/>
@@ -6224,22 +6875,24 @@
       <c r="U13" s="23"/>
       <c r="V13" s="23"/>
       <c r="W13" s="23"/>
-      <c r="X13" s="24"/>
+      <c r="X13" s="23"/>
       <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="24"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="B14" s="41"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="B15" s="41"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="B16" s="41"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="24"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="B14" s="40"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="B15" s="40"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="B16" s="40"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="40"/>
+      <c r="B17" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6253,15 +6906,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C15C6D-23FC-294D-A474-155EC8C1D970}">
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -6293,14 +6946,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -6332,39 +6987,41 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
       <c r="A4" s="8" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="B4" s="8"/>
     </row>
-    <row r="5" spans="1:27" ht="21" thickBot="1">
-      <c r="A5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="14"/>
+    <row r="5" spans="1:29" ht="21" thickBot="1">
+      <c r="A5" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="38" t="s">
+        <v>38</v>
+      </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+      <c r="H5" s="60"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="14"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="14"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
       <c r="Q5" s="14"/>
       <c r="R5" s="14"/>
       <c r="S5" s="14"/>
@@ -6375,12 +7032,16 @@
       <c r="X5" s="14"/>
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="15"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="38"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="15"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="32"/>
@@ -6388,12 +7049,12 @@
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="J6" s="32"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="42"/>
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
       <c r="S6" s="32"/>
@@ -6404,12 +7065,16 @@
       <c r="X6" s="32"/>
       <c r="Y6" s="32"/>
       <c r="Z6" s="32"/>
-      <c r="AA6" s="33"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="36"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
@@ -6417,12 +7082,12 @@
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="41"/>
       <c r="Q7" s="20"/>
       <c r="R7" s="20"/>
       <c r="S7" s="20"/>
@@ -6433,12 +7098,16 @@
       <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="36"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -6446,12 +7115,12 @@
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
       <c r="J8" s="20"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="41"/>
       <c r="Q8" s="20"/>
       <c r="R8" s="20"/>
       <c r="S8" s="20"/>
@@ -6462,12 +7131,16 @@
       <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="36"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
@@ -6475,12 +7148,12 @@
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="41"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
@@ -6491,12 +7164,16 @@
       <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="36"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
@@ -6504,12 +7181,12 @@
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="41"/>
       <c r="Q10" s="20"/>
       <c r="R10" s="20"/>
       <c r="S10" s="20"/>
@@ -6520,12 +7197,16 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="36"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
@@ -6533,12 +7214,12 @@
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="41"/>
       <c r="Q11" s="20"/>
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
@@ -6549,12 +7230,16 @@
       <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="36"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
@@ -6562,12 +7247,12 @@
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="41"/>
       <c r="Q12" s="20"/>
       <c r="R12" s="20"/>
       <c r="S12" s="20"/>
@@ -6578,48 +7263,110 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27" ht="21" thickBot="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="24"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="B14" s="41"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="B15" s="41"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="B16" s="41"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="67"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="64"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="66"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="67"/>
+    </row>
+    <row r="15" spans="1:29" ht="21" thickBot="1">
+      <c r="A15" s="63"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="24"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="B16" s="40"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="40"/>
+      <c r="B17" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6633,15 +7380,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA26C6E1-2A68-0F40-B671-B10830D9E135}">
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -6673,14 +7420,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -6712,33 +7461,35 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27" ht="21" thickBot="1">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="4" spans="1:29" ht="21" thickBot="1">
       <c r="A4" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="21" thickBot="1">
-      <c r="A5" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="21" thickBot="1">
+      <c r="A5" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+      <c r="H5" s="60"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
-      <c r="K5" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="38" t="s">
+        <v>39</v>
+      </c>
       <c r="N5" s="14"/>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
@@ -6752,14 +7503,16 @@
       <c r="X5" s="14"/>
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="15"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="A6" s="38">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="15"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="31"/>
       <c r="D6" s="32"/>
       <c r="E6" s="32"/>
       <c r="F6" s="32"/>
@@ -6767,10 +7520,10 @@
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="J6" s="32"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="43"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="32"/>
       <c r="O6" s="32"/>
       <c r="P6" s="32"/>
       <c r="Q6" s="32"/>
@@ -6783,14 +7536,16 @@
       <c r="X6" s="32"/>
       <c r="Y6" s="32"/>
       <c r="Z6" s="32"/>
-      <c r="AA6" s="33"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="A7" s="36">
-        <v>2</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="20"/>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
@@ -6798,10 +7553,10 @@
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="42"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
       <c r="O7" s="20"/>
       <c r="P7" s="20"/>
       <c r="Q7" s="20"/>
@@ -6814,14 +7569,16 @@
       <c r="X7" s="20"/>
       <c r="Y7" s="20"/>
       <c r="Z7" s="20"/>
-      <c r="AA7" s="21"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="36">
-        <v>3</v>
-      </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="21"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="20"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
@@ -6829,10 +7586,10 @@
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
       <c r="J8" s="20"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="42"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="20"/>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
       <c r="Q8" s="20"/>
@@ -6845,14 +7602,16 @@
       <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
       <c r="Z8" s="20"/>
-      <c r="AA8" s="21"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="A9" s="36">
-        <v>4</v>
-      </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="21"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
@@ -6860,10 +7619,10 @@
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
       <c r="J9" s="20"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="42"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="20"/>
       <c r="O9" s="20"/>
       <c r="P9" s="20"/>
       <c r="Q9" s="20"/>
@@ -6876,14 +7635,16 @@
       <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
-      <c r="AA9" s="21"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="36">
-        <v>5</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="21"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
@@ -6891,10 +7652,10 @@
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
       <c r="J10" s="20"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="42"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="20"/>
       <c r="O10" s="20"/>
       <c r="P10" s="20"/>
       <c r="Q10" s="20"/>
@@ -6907,14 +7668,16 @@
       <c r="X10" s="20"/>
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
-      <c r="AA10" s="21"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="A11" s="36">
-        <v>6</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="21"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
@@ -6922,10 +7685,10 @@
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="42"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="20"/>
       <c r="O11" s="20"/>
       <c r="P11" s="20"/>
       <c r="Q11" s="20"/>
@@ -6938,14 +7701,16 @@
       <c r="X11" s="20"/>
       <c r="Y11" s="20"/>
       <c r="Z11" s="20"/>
-      <c r="AA11" s="21"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="A12" s="36">
-        <v>7</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="21"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="62" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
@@ -6953,10 +7718,10 @@
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="42"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
       <c r="O12" s="20"/>
       <c r="P12" s="20"/>
       <c r="Q12" s="20"/>
@@ -6969,12 +7734,14 @@
       <c r="X12" s="20"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="20"/>
-      <c r="AA12" s="21"/>
-    </row>
-    <row r="13" spans="1:27" ht="21" thickBot="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="21"/>
+    </row>
+    <row r="13" spans="1:29" ht="21" thickBot="1">
+      <c r="A13" s="63"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="23"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
@@ -6982,9 +7749,9 @@
       <c r="H13" s="23"/>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="22"/>
       <c r="N13" s="23"/>
       <c r="O13" s="23"/>
       <c r="P13" s="23"/>
@@ -6998,7 +7765,9 @@
       <c r="X13" s="23"/>
       <c r="Y13" s="23"/>
       <c r="Z13" s="23"/>
-      <c r="AA13" s="24"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7012,15 +7781,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802CACCC-4B67-644C-9F76-EF5C50407AB5}">
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="4" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="21" thickBot="1">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:29" ht="21" thickBot="1">
+      <c r="A1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="9" t="str">
         <f>ProjectName</f>
         <v>【〇〇システム構築プロジェクト】</v>
@@ -7052,14 +7821,16 @@
       </c>
       <c r="Y1" s="10"/>
       <c r="Z1" s="10"/>
-      <c r="AA1" s="11"/>
-    </row>
-    <row r="2" spans="1:27" ht="21" thickBot="1">
-      <c r="A2" s="57" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="10"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:29" ht="21" thickBot="1">
+      <c r="A2" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="58"/>
       <c r="D2" s="5" t="str">
         <f>SystemName</f>
         <v>【システム】</v>
@@ -7091,56 +7862,944 @@
       </c>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="4" spans="1:27">
-      <c r="A4" s="8" t="s">
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="7"/>
+    </row>
+    <row r="3" spans="1:29" ht="21" thickBot="1"/>
+    <row r="4" spans="1:29">
+      <c r="A4" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="71" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="B5" s="41"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="B6" s="41"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="B7" s="41"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="B8" s="41"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="B9" s="41"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="B10" s="41"/>
-    </row>
-    <row r="11" spans="1:27">
-      <c r="B11" s="41"/>
-    </row>
-    <row r="12" spans="1:27">
-      <c r="B12" s="41"/>
-    </row>
-    <row r="13" spans="1:27">
-      <c r="B13" s="41"/>
-    </row>
-    <row r="14" spans="1:27">
-      <c r="B14" s="41"/>
-    </row>
-    <row r="15" spans="1:27">
-      <c r="B15" s="41"/>
-    </row>
-    <row r="16" spans="1:27">
-      <c r="B16" s="41"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="B17" s="40"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="70"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="70"/>
+      <c r="T4" s="70"/>
+      <c r="U4" s="70"/>
+      <c r="V4" s="70"/>
+      <c r="W4" s="70"/>
+      <c r="X4" s="70"/>
+      <c r="Y4" s="70"/>
+      <c r="Z4" s="70"/>
+      <c r="AA4" s="70"/>
+      <c r="AB4" s="70"/>
+      <c r="AC4" s="72"/>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="73"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="75"/>
+      <c r="U5" s="75"/>
+      <c r="V5" s="75"/>
+      <c r="W5" s="75"/>
+      <c r="X5" s="75"/>
+      <c r="Y5" s="75"/>
+      <c r="Z5" s="75"/>
+      <c r="AA5" s="75"/>
+      <c r="AB5" s="75"/>
+      <c r="AC5" s="76"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="73"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="76"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="75"/>
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="75"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="75"/>
+      <c r="AC6" s="76"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="76"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75"/>
+      <c r="X7" s="75"/>
+      <c r="Y7" s="75"/>
+      <c r="Z7" s="75"/>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="75"/>
+      <c r="AC7" s="76"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="73"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="76"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="75"/>
+      <c r="R8" s="75"/>
+      <c r="S8" s="75"/>
+      <c r="T8" s="75"/>
+      <c r="U8" s="75"/>
+      <c r="V8" s="75"/>
+      <c r="W8" s="75"/>
+      <c r="X8" s="75"/>
+      <c r="Y8" s="75"/>
+      <c r="Z8" s="75"/>
+      <c r="AA8" s="75"/>
+      <c r="AB8" s="75"/>
+      <c r="AC8" s="76"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="73"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="75"/>
+      <c r="V9" s="75"/>
+      <c r="W9" s="75"/>
+      <c r="X9" s="75"/>
+      <c r="Y9" s="75"/>
+      <c r="Z9" s="75"/>
+      <c r="AA9" s="75"/>
+      <c r="AB9" s="75"/>
+      <c r="AC9" s="76"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="73"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
+      <c r="V10" s="75"/>
+      <c r="W10" s="75"/>
+      <c r="X10" s="75"/>
+      <c r="Y10" s="75"/>
+      <c r="Z10" s="75"/>
+      <c r="AA10" s="75"/>
+      <c r="AB10" s="75"/>
+      <c r="AC10" s="76"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="76"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="75"/>
+      <c r="T11" s="75"/>
+      <c r="U11" s="75"/>
+      <c r="V11" s="75"/>
+      <c r="W11" s="75"/>
+      <c r="X11" s="75"/>
+      <c r="Y11" s="75"/>
+      <c r="Z11" s="75"/>
+      <c r="AA11" s="75"/>
+      <c r="AB11" s="75"/>
+      <c r="AC11" s="76"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="73"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="75"/>
+      <c r="N12" s="76"/>
+      <c r="O12" s="75"/>
+      <c r="P12" s="75"/>
+      <c r="Q12" s="75"/>
+      <c r="R12" s="75"/>
+      <c r="S12" s="75"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="75"/>
+      <c r="V12" s="75"/>
+      <c r="W12" s="75"/>
+      <c r="X12" s="75"/>
+      <c r="Y12" s="75"/>
+      <c r="Z12" s="75"/>
+      <c r="AA12" s="75"/>
+      <c r="AB12" s="75"/>
+      <c r="AC12" s="76"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="73"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="76"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="75"/>
+      <c r="Q13" s="75"/>
+      <c r="R13" s="75"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="75"/>
+      <c r="V13" s="75"/>
+      <c r="W13" s="75"/>
+      <c r="X13" s="75"/>
+      <c r="Y13" s="75"/>
+      <c r="Z13" s="75"/>
+      <c r="AA13" s="75"/>
+      <c r="AB13" s="75"/>
+      <c r="AC13" s="76"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="73"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="75"/>
+      <c r="M14" s="75"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="75"/>
+      <c r="P14" s="75"/>
+      <c r="Q14" s="75"/>
+      <c r="R14" s="75"/>
+      <c r="S14" s="75"/>
+      <c r="T14" s="75"/>
+      <c r="U14" s="75"/>
+      <c r="V14" s="75"/>
+      <c r="W14" s="75"/>
+      <c r="X14" s="75"/>
+      <c r="Y14" s="75"/>
+      <c r="Z14" s="75"/>
+      <c r="AA14" s="75"/>
+      <c r="AB14" s="75"/>
+      <c r="AC14" s="76"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="73"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="75"/>
+      <c r="Q15" s="75"/>
+      <c r="R15" s="75"/>
+      <c r="S15" s="75"/>
+      <c r="T15" s="75"/>
+      <c r="U15" s="75"/>
+      <c r="V15" s="75"/>
+      <c r="W15" s="75"/>
+      <c r="X15" s="75"/>
+      <c r="Y15" s="75"/>
+      <c r="Z15" s="75"/>
+      <c r="AA15" s="75"/>
+      <c r="AB15" s="75"/>
+      <c r="AC15" s="76"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="73"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="75"/>
+      <c r="Q16" s="75"/>
+      <c r="R16" s="75"/>
+      <c r="S16" s="75"/>
+      <c r="T16" s="75"/>
+      <c r="U16" s="75"/>
+      <c r="V16" s="75"/>
+      <c r="W16" s="75"/>
+      <c r="X16" s="75"/>
+      <c r="Y16" s="75"/>
+      <c r="Z16" s="75"/>
+      <c r="AA16" s="75"/>
+      <c r="AB16" s="75"/>
+      <c r="AC16" s="76"/>
+    </row>
+    <row r="17" spans="1:29">
+      <c r="A17" s="73"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="75"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="75"/>
+      <c r="N17" s="76"/>
+      <c r="O17" s="75"/>
+      <c r="P17" s="75"/>
+      <c r="Q17" s="75"/>
+      <c r="R17" s="75"/>
+      <c r="S17" s="75"/>
+      <c r="T17" s="75"/>
+      <c r="U17" s="75"/>
+      <c r="V17" s="75"/>
+      <c r="W17" s="75"/>
+      <c r="X17" s="75"/>
+      <c r="Y17" s="75"/>
+      <c r="Z17" s="75"/>
+      <c r="AA17" s="75"/>
+      <c r="AB17" s="75"/>
+      <c r="AC17" s="76"/>
+    </row>
+    <row r="18" spans="1:29">
+      <c r="A18" s="73"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="75"/>
+      <c r="S18" s="75"/>
+      <c r="T18" s="75"/>
+      <c r="U18" s="75"/>
+      <c r="V18" s="75"/>
+      <c r="W18" s="75"/>
+      <c r="X18" s="75"/>
+      <c r="Y18" s="75"/>
+      <c r="Z18" s="75"/>
+      <c r="AA18" s="75"/>
+      <c r="AB18" s="75"/>
+      <c r="AC18" s="76"/>
+    </row>
+    <row r="19" spans="1:29">
+      <c r="A19" s="78"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="75"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="75"/>
+      <c r="R19" s="75"/>
+      <c r="S19" s="75"/>
+      <c r="T19" s="75"/>
+      <c r="U19" s="75"/>
+      <c r="V19" s="75"/>
+      <c r="W19" s="75"/>
+      <c r="X19" s="75"/>
+      <c r="Y19" s="75"/>
+      <c r="Z19" s="75"/>
+      <c r="AA19" s="75"/>
+      <c r="AB19" s="75"/>
+      <c r="AC19" s="76"/>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20" s="73"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="75"/>
+      <c r="K20" s="75"/>
+      <c r="L20" s="75"/>
+      <c r="M20" s="75"/>
+      <c r="N20" s="76"/>
+      <c r="O20" s="75"/>
+      <c r="P20" s="75"/>
+      <c r="Q20" s="75"/>
+      <c r="R20" s="75"/>
+      <c r="S20" s="75"/>
+      <c r="T20" s="75"/>
+      <c r="U20" s="75"/>
+      <c r="V20" s="75"/>
+      <c r="W20" s="75"/>
+      <c r="X20" s="75"/>
+      <c r="Y20" s="75"/>
+      <c r="Z20" s="75"/>
+      <c r="AA20" s="75"/>
+      <c r="AB20" s="75"/>
+      <c r="AC20" s="76"/>
+    </row>
+    <row r="21" spans="1:29">
+      <c r="A21" s="73"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="75"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="75"/>
+      <c r="P21" s="75"/>
+      <c r="Q21" s="75"/>
+      <c r="R21" s="75"/>
+      <c r="S21" s="75"/>
+      <c r="T21" s="75"/>
+      <c r="U21" s="75"/>
+      <c r="V21" s="75"/>
+      <c r="W21" s="75"/>
+      <c r="X21" s="75"/>
+      <c r="Y21" s="75"/>
+      <c r="Z21" s="75"/>
+      <c r="AA21" s="75"/>
+      <c r="AB21" s="75"/>
+      <c r="AC21" s="76"/>
+    </row>
+    <row r="22" spans="1:29">
+      <c r="A22" s="73"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="75"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="75"/>
+      <c r="L22" s="75"/>
+      <c r="M22" s="75"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="75"/>
+      <c r="P22" s="75"/>
+      <c r="Q22" s="75"/>
+      <c r="R22" s="75"/>
+      <c r="S22" s="75"/>
+      <c r="T22" s="75"/>
+      <c r="U22" s="75"/>
+      <c r="V22" s="75"/>
+      <c r="W22" s="75"/>
+      <c r="X22" s="75"/>
+      <c r="Y22" s="75"/>
+      <c r="Z22" s="75"/>
+      <c r="AA22" s="75"/>
+      <c r="AB22" s="75"/>
+      <c r="AC22" s="76"/>
+    </row>
+    <row r="23" spans="1:29">
+      <c r="A23" s="73"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="75"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="75"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="75"/>
+      <c r="R23" s="75"/>
+      <c r="S23" s="75"/>
+      <c r="T23" s="75"/>
+      <c r="U23" s="75"/>
+      <c r="V23" s="75"/>
+      <c r="W23" s="75"/>
+      <c r="X23" s="75"/>
+      <c r="Y23" s="75"/>
+      <c r="Z23" s="75"/>
+      <c r="AA23" s="75"/>
+      <c r="AB23" s="75"/>
+      <c r="AC23" s="76"/>
+    </row>
+    <row r="24" spans="1:29">
+      <c r="A24" s="73"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="76"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="75"/>
+      <c r="T24" s="75"/>
+      <c r="U24" s="75"/>
+      <c r="V24" s="75"/>
+      <c r="W24" s="75"/>
+      <c r="X24" s="75"/>
+      <c r="Y24" s="75"/>
+      <c r="Z24" s="75"/>
+      <c r="AA24" s="75"/>
+      <c r="AB24" s="75"/>
+      <c r="AC24" s="76"/>
+    </row>
+    <row r="25" spans="1:29">
+      <c r="A25" s="73"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="75"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="75"/>
+      <c r="X25" s="75"/>
+      <c r="Y25" s="75"/>
+      <c r="Z25" s="75"/>
+      <c r="AA25" s="75"/>
+      <c r="AB25" s="75"/>
+      <c r="AC25" s="76"/>
+    </row>
+    <row r="26" spans="1:29">
+      <c r="A26" s="73"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="75"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="75"/>
+      <c r="X26" s="75"/>
+      <c r="Y26" s="75"/>
+      <c r="Z26" s="75"/>
+      <c r="AA26" s="75"/>
+      <c r="AB26" s="75"/>
+      <c r="AC26" s="76"/>
+    </row>
+    <row r="27" spans="1:29">
+      <c r="A27" s="73"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="75"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="75"/>
+      <c r="N27" s="76"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="75"/>
+      <c r="S27" s="75"/>
+      <c r="T27" s="75"/>
+      <c r="U27" s="75"/>
+      <c r="V27" s="75"/>
+      <c r="W27" s="75"/>
+      <c r="X27" s="75"/>
+      <c r="Y27" s="75"/>
+      <c r="Z27" s="75"/>
+      <c r="AA27" s="75"/>
+      <c r="AB27" s="75"/>
+      <c r="AC27" s="76"/>
+    </row>
+    <row r="28" spans="1:29">
+      <c r="A28" s="73"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="75"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="75"/>
+      <c r="K28" s="75"/>
+      <c r="L28" s="75"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="75"/>
+      <c r="R28" s="75"/>
+      <c r="S28" s="75"/>
+      <c r="T28" s="75"/>
+      <c r="U28" s="75"/>
+      <c r="V28" s="75"/>
+      <c r="W28" s="75"/>
+      <c r="X28" s="75"/>
+      <c r="Y28" s="75"/>
+      <c r="Z28" s="75"/>
+      <c r="AA28" s="75"/>
+      <c r="AB28" s="75"/>
+      <c r="AC28" s="76"/>
+    </row>
+    <row r="29" spans="1:29">
+      <c r="A29" s="73"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="75"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="75"/>
+      <c r="K29" s="75"/>
+      <c r="L29" s="75"/>
+      <c r="M29" s="75"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="75"/>
+      <c r="P29" s="75"/>
+      <c r="Q29" s="75"/>
+      <c r="R29" s="75"/>
+      <c r="S29" s="75"/>
+      <c r="T29" s="75"/>
+      <c r="U29" s="75"/>
+      <c r="V29" s="75"/>
+      <c r="W29" s="75"/>
+      <c r="X29" s="75"/>
+      <c r="Y29" s="75"/>
+      <c r="Z29" s="75"/>
+      <c r="AA29" s="75"/>
+      <c r="AB29" s="75"/>
+      <c r="AC29" s="76"/>
+    </row>
+    <row r="30" spans="1:29">
+      <c r="A30" s="73"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="75"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="75"/>
+      <c r="L30" s="75"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="75"/>
+      <c r="P30" s="75"/>
+      <c r="Q30" s="75"/>
+      <c r="R30" s="75"/>
+      <c r="S30" s="75"/>
+      <c r="T30" s="75"/>
+      <c r="U30" s="75"/>
+      <c r="V30" s="75"/>
+      <c r="W30" s="75"/>
+      <c r="X30" s="75"/>
+      <c r="Y30" s="75"/>
+      <c r="Z30" s="75"/>
+      <c r="AA30" s="75"/>
+      <c r="AB30" s="75"/>
+      <c r="AC30" s="76"/>
+    </row>
+    <row r="31" spans="1:29">
+      <c r="A31" s="73"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="75"/>
+      <c r="Q31" s="75"/>
+      <c r="R31" s="75"/>
+      <c r="S31" s="75"/>
+      <c r="T31" s="75"/>
+      <c r="U31" s="75"/>
+      <c r="V31" s="75"/>
+      <c r="W31" s="75"/>
+      <c r="X31" s="75"/>
+      <c r="Y31" s="75"/>
+      <c r="Z31" s="75"/>
+      <c r="AA31" s="75"/>
+      <c r="AB31" s="75"/>
+      <c r="AC31" s="76"/>
+    </row>
+    <row r="32" spans="1:29">
+      <c r="A32" s="73"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="75"/>
+      <c r="L32" s="75"/>
+      <c r="M32" s="75"/>
+      <c r="N32" s="76"/>
+      <c r="O32" s="75"/>
+      <c r="P32" s="75"/>
+      <c r="Q32" s="75"/>
+      <c r="R32" s="75"/>
+      <c r="S32" s="75"/>
+      <c r="T32" s="75"/>
+      <c r="U32" s="75"/>
+      <c r="V32" s="75"/>
+      <c r="W32" s="75"/>
+      <c r="X32" s="75"/>
+      <c r="Y32" s="75"/>
+      <c r="Z32" s="75"/>
+      <c r="AA32" s="75"/>
+      <c r="AB32" s="75"/>
+      <c r="AC32" s="76"/>
+    </row>
+    <row r="33" spans="1:29" ht="21" thickBot="1">
+      <c r="A33" s="5"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
